--- a/server/excel/release/destiny-dungeon.xlsx
+++ b/server/excel/release/destiny-dungeon.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="命格副本关卡" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="命格副本章节" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="命格副本宝箱" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="命格关卡挑战" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="命格章节路径" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命格副本关卡" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命格副本章节" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命格副本宝箱" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命格关卡挑战" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="命格章节路径" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -739,190 +739,190 @@
     <t xml:space="preserve">6:10113:1#3:100059:1</t>
   </si>
   <si>
-    <t xml:space="preserve">Chiến đấu thắng lợi</t>
+    <t xml:space="preserve">Thắng trận</t>
   </si>
   <si>
     <t xml:space="preserve">Nói rõ một chút kiểm trắc thao tác</t>
   </si>
   <si>
-    <t xml:space="preserve">Thời gian chiến đấu không cao hơn &lt;2214 14&gt; Hiệp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thời gian chiến đấu không cao hơn &lt;2214 6&gt; Hiệp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thời gian chiến đấu không cao hơn &lt;2214 8&gt; Hiệp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Phục long trận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Cự ngựa trận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Linh xà trận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Sừng hươu trận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Khóa yêu trận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sử dụng &lt;2214 Nhạn linh trận &gt; Đạt được thắng lợi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không được với trận &lt;2214 Pháp sư &gt; Tướng</t>
+    <t xml:space="preserve">Thắng trong vòng &lt;2214 14&gt; hiệp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng trong vòng &lt;2214 6&gt; hiệp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng trong vòng &lt;2214 8&gt; hiệp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Lục&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Cam&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Vàng&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Tím&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Lam&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thắng bằng trận hình &lt;2214 Đỏ&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không ra trận tướng &lt;2214 Magic&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Cùng nhiệm vụ yêu cầu số liệu</t>
   </si>
   <si>
-    <t xml:space="preserve">Không được với trận &lt;2214 Phụ trợ &gt; Tướng</t>
+    <t xml:space="preserve">Không ra trận tướng &lt;2214 Buff&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Tướng thỏa mãn</t>
   </si>
   <si>
-    <t xml:space="preserve">Không được với trận &lt;2214 Xe tăng &gt; Tướng</t>
+    <t xml:space="preserve">Không ra trận tướng &lt;2214 Tank&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">0: Kiểm trắc giá trị = Mục tiêu giá trị</t>
   </si>
   <si>
-    <t xml:space="preserve">Không được với trận &lt;2214 Chiến sĩ &gt; Tướng</t>
+    <t xml:space="preserve">Không ra trận tướng &lt;2214 Dame&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">1: Kiểm trắc giá trị &lt;= Mục tiêu giá trị</t>
   </si>
   <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Pháp sư &gt; Tướng không cao hơn &lt;2214 1&gt; Cái</t>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 1&gt; tướng &lt;2214 Magic&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">2: Kiểm trắc giá trị &gt;= Mục tiêu giá trị</t>
   </si>
   <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Pháp sư &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Magic&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Lúc nào sẽ dùng đến 1 Đâu?</t>
   </si>
   <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Phụ trợ &gt; Tướng không cao hơn &lt;2214 1&gt; Cái</t>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 1&gt; tướng &lt;2214 Buff&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Tỉ như 3 Hiệp bên trong thông quan</t>
   </si>
   <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Phụ trợ &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Xe tăng &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Chiến sĩ &gt; Tướng không cao hơn &lt;2214 1&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Chiến sĩ &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái chiến sĩ &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái pháp sư &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái phụ trợ &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái xe tăng &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái pháp sư &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái phụ trợ &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái xe tăng &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái chiến sĩ &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 3 Cái xe tăng &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Không được với trận &lt;2214 Thần tộc &gt; Tướng</t>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Buff&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Tank&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 1&gt; tướng &lt;2214 Dame&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Dame&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Dame&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Magic&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Buff&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Tank&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Magic&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Buff&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Tank&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Dame&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 3&gt; tướng &lt;2214 Tank&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không ra trận tướng &lt;2214 Hải Quân&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Mai nâng như sau:</t>
   </si>
   <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Ma tộc &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Nhân tộc &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Thần tộc &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Tiên Tộc &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ra trận &lt;2214 Yêu tộc &gt; Tướng không cao hơn &lt;2214 2&gt; Cái</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái ma tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái nhân tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái Thần tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái Tiên Tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 1 Cái yêu tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái ma tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái nhân tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái Thần tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái Tiên Tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 2 Cái yêu tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 3 Cái ma tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 3 Cái nhân tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 3 Cái yêu tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chí ít ra trận &lt;2214 5 Cái Tiên Tộc &gt; Tướng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bổn tràng chiến đấu không đồng đội tử vong</t>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Ngũ Hoàng&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Tân Binh&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Hải Quân&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Hải Tặc&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận tối đa &lt;2214 2&gt; tướng &lt;2214 Dũng Sĩ&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Ngũ Hoàng&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Tân Binh&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Hải Quân&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Hải Tặc&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 1&gt; tướng &lt;2214 Dũng Sĩ&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Ngũ Hoàng&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Tân Binh&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Hải Quân&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Hải Tặc&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 2&gt; tướng &lt;2214 Dũng Sĩ&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 3&gt; tướng &lt;2214 Ngũ Hoàng&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 3&gt; tướng &lt;2214 Tân Binh&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 3&gt; tướng &lt;2214 Dũng Sĩ&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ra trận ít nhất &lt;2214 5&gt; tướng &lt;2214 Hải Tặc&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không có đồng đội tử trận</t>
   </si>
   <si>
     <t xml:space="preserve">Là chỉ như thế nào phán đoán số liệu</t>
   </si>
   <si>
-    <t xml:space="preserve">Thắng lợi lúc tất cả tướng huyết lượng tại &lt;2214 50%&gt; Trở lên</t>
+    <t xml:space="preserve">Khi thắng, mọi tướng còn từ &lt;2214 50%&gt; HP</t>
   </si>
   <si>
     <t xml:space="preserve">路径图</t>
